--- a/신고신저가_20260723.xlsx
+++ b/신고신저가_20260723.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -74,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -449,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -607,7 +609,49 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 지난주 AI반도체 급락이 미국·중국서 하루 만에 반등 — SMCI 대규모 수주가 트리거로 미 반도체 랠리(SOX +5.2%), 중국A 신저 41→0 급반전. 단 온기가 일본·홍콩엔 미전달, 미·이란 지정학이 금·엔·유가로 번지는 중.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 美: S&amp;P +0.9%·나스닥 +1.3% 반등(SMCI 수주 600억달러+SpaceX AI데이터센터) — 신고 32 vs 신저 8. 강세: 금융 순증 +8·에너지 +5·유틸 +4. ARWR 임상 호성적 +19%, WAB 실적상회 +10%. 약세: TE커넥티비티 인수우려 -4%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 日: 닛케이 -0.17% 도지 — 오전 +1,200엔 급등분을 엔약세(163엔, 39년래 최저)·유가로 오후 전량 반납. 신고 9개 전부 금융(SMFG·재팬포스트뱅크·MS&amp;AD) — 금리·엔약세 수혜 로테이션.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩: 항셍 -0.95%·항셍테크 -2~3% — 미 반도체 랠리 온기 미전달, 滔搏 -24% 심리 압박. 신고는 캐세이·HSBC 등 경기민감·금융뿐.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 中: 상해 +0.5% — 자사주매입·기관 자기매수 재개가 지지, 신저 0 급반전. 반도체·네트워킹 주도(루이지에 +13.7%), 단 화홍은 미 수출통제로 -1.9%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①오늘밤 미국 반도체 랠리 지속성 ②엔 163엔 개입 경계 ③금·유가(미·이란) 인플레 재점화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -708,7 +752,7 @@
       <c r="F2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -743,7 +787,7 @@
       <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -778,7 +822,7 @@
       <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -813,7 +857,7 @@
       <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -848,7 +892,7 @@
       <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -883,7 +927,7 @@
       <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -918,7 +962,7 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -953,7 +997,7 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -988,7 +1032,7 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1023,7 +1067,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1058,7 +1102,7 @@
       <c r="F12" t="n">
         <v>-1</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1093,7 +1137,7 @@
       <c r="F13" t="n">
         <v>-1</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1128,7 +1172,7 @@
       <c r="F14" t="n">
         <v>-1</v>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1408,7 +1452,7 @@
       <c r="F22" t="n">
         <v>7</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1443,7 +1487,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1478,7 +1522,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2038,7 +2082,7 @@
       <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2073,7 +2117,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2108,7 +2152,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2143,7 +2187,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2668,7 +2712,7 @@
       <c r="F58" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2703,7 +2747,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2738,7 +2782,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3439,55 +3483,55 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="6" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="6" t="n">
         <v>-6.2</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="6" t="n">
         <v>16.7</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="6" t="n">
         <v>25.5</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="6" t="n">
         <v>24.6</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="6" t="n">
         <v>21.6</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="6" t="n">
         <v>56</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="6" t="n">
         <v>-27.7</v>
       </c>
       <c r="Q2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="6" t="n">
         <v>34.7</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="T2" s="6" t="n">
         <v>43.6</v>
       </c>
       <c r="U2" t="n">
@@ -3510,55 +3554,55 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="6" t="n">
         <v>6.2</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="6" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="6" t="n">
         <v>3.9</v>
       </c>
       <c r="I3" t="n">
         <v>8</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="6" t="n">
         <v>14.5</v>
       </c>
       <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="6" t="n">
         <v>-2.1</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="6" t="n">
         <v>26</v>
       </c>
       <c r="S3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="T3" s="6" t="n">
         <v>13.3</v>
       </c>
       <c r="U3" t="n">
@@ -3581,55 +3625,55 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="6" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="6" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="6" t="n">
         <v>3.2</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="6" t="n">
         <v>14.9</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="6" t="n">
         <v>30.6</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="6" t="n">
         <v>12</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="6" t="n">
         <v>-10.6</v>
       </c>
       <c r="Q4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="6" t="n">
         <v>34.8</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="T4" s="6" t="n">
         <v>-1.7</v>
       </c>
       <c r="U4" t="n">
@@ -3652,55 +3696,55 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="6" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="6" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="6" t="n">
         <v>-4</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="6" t="n">
         <v>-4.1</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="6" t="n">
         <v>7.4</v>
       </c>
       <c r="K5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="6" t="n">
         <v>26.5</v>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="6" t="n">
         <v>39.6</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="P5" s="6" t="n">
         <v>-36.3</v>
       </c>
       <c r="Q5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="R5" s="6" t="n">
         <v>27.9</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="T5" s="6" t="n">
         <v>29.6</v>
       </c>
       <c r="U5" t="n">
@@ -3723,55 +3767,55 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="6" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="6" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="6" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="6" t="n">
         <v>-6.7</v>
       </c>
       <c r="I6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="6" t="n">
         <v>23.1</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="6" t="n">
         <v>34.7</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="6" t="n">
         <v>52.8</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="6" t="n">
         <v>-37.6</v>
       </c>
       <c r="Q6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R6" s="6" t="n">
         <v>16</v>
       </c>
       <c r="S6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="T6" s="6" t="n">
         <v>26.9</v>
       </c>
       <c r="U6" t="n">
@@ -3794,55 +3838,55 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="6" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="6" t="n">
         <v>15.9</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="6" t="n">
         <v>19.3</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="6" t="n">
         <v>17.3</v>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="6" t="n">
         <v>18.1</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="P7" s="6" t="n">
         <v>-5.6</v>
       </c>
       <c r="Q7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="R7" s="6" t="n">
         <v>21.1</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="T7" s="6" t="n">
         <v>10.9</v>
       </c>
       <c r="U7" t="n">
@@ -3865,55 +3909,55 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="6" t="n">
         <v>2.7</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="6" t="n">
         <v>3.8</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="6" t="n">
         <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="6" t="n">
         <v>12.2</v>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="6" t="n">
         <v>-0.8</v>
       </c>
       <c r="O8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="6" t="n">
         <v>-0.8</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="R8" s="6" t="n">
         <v>17.2</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="T8" s="6" t="n">
         <v>10.1</v>
       </c>
       <c r="U8" t="n">
@@ -3936,55 +3980,55 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="6" t="n">
         <v>6.7</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="6" t="n">
         <v>34.2</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="6" t="n">
         <v>7.9</v>
       </c>
       <c r="K9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="6" t="n">
         <v>-0.6</v>
       </c>
       <c r="O9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="P9" s="6" t="n">
         <v>64.3</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="R9" s="6" t="n">
         <v>53.3</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="T9" s="6" t="n">
         <v>-32.7</v>
       </c>
       <c r="U9" t="n">
@@ -4007,55 +4051,55 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="6" t="n">
         <v>2.7</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="I10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="6" t="n">
         <v>16</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="6" t="n">
         <v>23.3</v>
       </c>
       <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="6" t="n">
         <v>-7.2</v>
       </c>
       <c r="O10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="P10" s="6" t="n">
         <v>1.4</v>
       </c>
       <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="R10" s="6" t="n">
         <v>17.7</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="T10" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="U10" t="n">
@@ -4078,55 +4122,55 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="6" t="n">
         <v>1.4</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="6" t="n">
         <v>13</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="6" t="n">
         <v>9.9</v>
       </c>
       <c r="K11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="6" t="n">
         <v>12.5</v>
       </c>
       <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="P11" s="6" t="n">
         <v>-12.3</v>
       </c>
       <c r="Q11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="R11" s="6" t="n">
         <v>27.4</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="6" t="n">
         <v>20.5</v>
       </c>
       <c r="U11" t="n">
@@ -4149,55 +4193,55 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="6" t="n">
         <v>3.7</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="6" t="n">
         <v>13.3</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="6" t="n">
         <v>2.6</v>
       </c>
       <c r="K12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="6" t="n">
         <v>5.1</v>
       </c>
       <c r="M12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="6" t="n">
         <v>12.4</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="P12" s="6" t="n">
         <v>-26.2</v>
       </c>
       <c r="Q12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="R12" s="6" t="n">
         <v>46.1</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="T12" s="6" t="n">
         <v>-2.2</v>
       </c>
       <c r="U12" t="n">
@@ -4220,55 +4264,55 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="6" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="6" t="n">
         <v>7.4</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="6" t="n">
         <v>16.7</v>
       </c>
       <c r="I13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="6" t="n">
         <v>11.8</v>
       </c>
       <c r="K13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N13" s="6" t="n">
         <v>22.3</v>
       </c>
       <c r="O13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="P13" s="6" t="n">
         <v>6.4</v>
       </c>
       <c r="Q13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="R13" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="S13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="T13" s="6" t="n">
         <v>-3.4</v>
       </c>
       <c r="U13" t="n">
@@ -4291,55 +4335,55 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="6" t="n">
         <v>7.1</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="6" t="n">
         <v>5.4</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="6" t="n">
         <v>-7.8</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="6" t="n">
         <v>15.6</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="6" t="n">
         <v>41.4</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="6" t="n">
         <v>29.9</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="6" t="n">
         <v>37.2</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="P14" s="6" t="n">
         <v>23.6</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="R14" s="6" t="n">
         <v>39.3</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="T14" s="6" t="n">
         <v>-29</v>
       </c>
       <c r="U14" t="n">
@@ -4362,55 +4406,55 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="6" t="n">
         <v>-5.8</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="6" t="n">
         <v>11.1</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="6" t="n">
         <v>42</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="6" t="n">
         <v>21.6</v>
       </c>
       <c r="M15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="6" t="n">
         <v>32</v>
       </c>
       <c r="O15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="P15" s="6" t="n">
         <v>-2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="R15" s="6" t="n">
         <v>12.6</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="T15" s="6" t="n">
         <v>-6.1</v>
       </c>
       <c r="U15" t="n">
@@ -4433,55 +4477,55 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="6" t="n">
         <v>-0</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="6" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="6" t="n">
         <v>7.4</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="6" t="n">
         <v>24.2</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="6" t="n">
         <v>8.6</v>
       </c>
       <c r="K16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="6" t="n">
         <v>3.9</v>
       </c>
       <c r="M16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="6" t="n">
         <v>23.1</v>
       </c>
       <c r="O16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="P16" s="6" t="n">
         <v>-9.4</v>
       </c>
       <c r="Q16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="R16" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="S16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="T16" s="6" t="n">
         <v>8.6</v>
       </c>
       <c r="U16" t="n">
@@ -4504,55 +4548,55 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="6" t="n">
         <v>3.2</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="6" t="n">
         <v>-6.4</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="I17" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="6" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="6" t="n">
         <v>10.8</v>
       </c>
       <c r="M17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="O17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="P17" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="R17" s="6" t="n">
         <v>-8.4</v>
       </c>
       <c r="S17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="T17" s="6" t="n">
         <v>4.6</v>
       </c>
       <c r="U17" t="n">
@@ -4575,55 +4619,55 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="6" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="6" t="n">
         <v>3.8</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="6" t="n">
         <v>5.2</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="6" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="6" t="n">
         <v>-5.5</v>
       </c>
       <c r="I18" t="n">
         <v>17</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="6" t="n">
         <v>13.5</v>
       </c>
       <c r="K18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="M18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="6" t="n">
         <v>40.5</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="P18" s="6" t="n">
         <v>-10.7</v>
       </c>
       <c r="Q18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="R18" s="6" t="n">
         <v>27.8</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="T18" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="U18" t="n">
@@ -4646,55 +4690,55 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="6" t="n">
         <v>-29.2</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="6" t="n">
         <v>-12.3</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="6" t="n">
         <v>68.8</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="6" t="n">
         <v>20.6</v>
       </c>
       <c r="M19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="6" t="n">
         <v>35</v>
       </c>
       <c r="O19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="P19" s="6" t="n">
         <v>16.1</v>
       </c>
       <c r="Q19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="R19" s="6" t="n">
         <v>20.8</v>
       </c>
       <c r="S19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="T19" s="6" t="n">
         <v>-8.6</v>
       </c>
       <c r="U19" t="n">
@@ -4717,55 +4761,55 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="6" t="n">
         <v>-0</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="6" t="n">
         <v>-6.1</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="6" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="6" t="n">
         <v>20</v>
       </c>
       <c r="I20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="6" t="n">
         <v>31.1</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="6" t="n">
         <v>22.3</v>
       </c>
       <c r="M20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="6" t="n">
         <v>33.9</v>
       </c>
       <c r="O20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="P20" s="6" t="n">
         <v>-9.9</v>
       </c>
       <c r="Q20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="4" t="n">
+      <c r="R20" s="6" t="n">
         <v>7.5</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="T20" s="6" t="n">
         <v>17.7</v>
       </c>
       <c r="U20" t="n">
@@ -4788,55 +4832,55 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="6" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="6" t="n">
         <v>-11.3</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="6" t="n">
         <v>15.8</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="6" t="n">
         <v>31.8</v>
       </c>
       <c r="I21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="6" t="n">
         <v>27.5</v>
       </c>
       <c r="K21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="6" t="n">
         <v>17.9</v>
       </c>
       <c r="M21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="6" t="n">
         <v>33.7</v>
       </c>
       <c r="O21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="P21" s="6" t="n">
         <v>-23</v>
       </c>
       <c r="Q21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="R21" s="6" t="n">
         <v>25</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="T21" s="6" t="n">
         <v>26.2</v>
       </c>
       <c r="U21" t="n">
@@ -4859,55 +4903,55 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="6" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="6" t="n">
         <v>1.7</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="6" t="n">
         <v>4.6</v>
       </c>
       <c r="I22" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" s="6" t="n">
         <v>13.9</v>
       </c>
       <c r="K22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="6" t="n">
         <v>21</v>
       </c>
       <c r="M22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="6" t="n">
         <v>17.9</v>
       </c>
       <c r="O22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="P22" s="6" t="n">
         <v>-5.9</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="4" t="n">
+      <c r="R22" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="S22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="4" t="n">
+      <c r="T22" s="6" t="n">
         <v>21.9</v>
       </c>
       <c r="U22" t="n">
@@ -4930,55 +4974,55 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="6" t="n">
         <v>-7.6</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="6" t="n">
         <v>1.9</v>
       </c>
       <c r="I23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="6" t="n">
         <v>37.4</v>
       </c>
       <c r="K23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="6" t="n">
         <v>6.3</v>
       </c>
       <c r="M23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="6" t="n">
         <v>35</v>
       </c>
       <c r="O23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="P23" s="6" t="n">
         <v>13.2</v>
       </c>
       <c r="Q23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="R23" s="6" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="S23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="T23" s="6" t="n">
         <v>-10.7</v>
       </c>
       <c r="U23" t="n">
@@ -5001,55 +5045,55 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="6" t="n">
         <v>4.7</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="6" t="n">
         <v>9.1</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="6" t="n">
         <v>3.2</v>
       </c>
       <c r="I24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="6" t="n">
         <v>19.9</v>
       </c>
       <c r="K24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="6" t="n">
         <v>-0</v>
       </c>
       <c r="M24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="6" t="n">
         <v>19</v>
       </c>
       <c r="O24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="P24" s="6" t="n">
         <v>13.1</v>
       </c>
       <c r="Q24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="4" t="n">
+      <c r="R24" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="S24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="T24" s="6" t="n">
         <v>-17.1</v>
       </c>
       <c r="U24" t="n">
@@ -5072,55 +5116,55 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="6" t="n">
         <v>6.4</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="6" t="n">
         <v>4.7</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="6" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="6" t="n">
         <v>15.5</v>
       </c>
       <c r="I25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="6" t="n">
         <v>41.5</v>
       </c>
       <c r="K25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="6" t="n">
         <v>20.1</v>
       </c>
       <c r="M25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="6" t="n">
         <v>42</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="P25" s="6" t="n">
         <v>21.3</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="R25" s="6" t="n">
         <v>29.2</v>
       </c>
       <c r="S25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="T25" s="6" t="n">
         <v>1.9</v>
       </c>
       <c r="U25" t="n">
@@ -5143,55 +5187,55 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="6" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="6" t="n">
         <v>4.1</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="6" t="n">
         <v>1.7</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="6" t="n">
         <v>3.2</v>
       </c>
       <c r="I26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="J26" s="6" t="n">
         <v>16.8</v>
       </c>
       <c r="K26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="6" t="n">
         <v>23.4</v>
       </c>
       <c r="M26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="P26" s="6" t="n">
         <v>10.2</v>
       </c>
       <c r="Q26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="4" t="n">
+      <c r="R26" s="6" t="n">
         <v>-4.4</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="T26" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="U26" t="n">
@@ -5214,55 +5258,55 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="6" t="n">
         <v>24.5</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="6" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="6" t="n">
         <v>44.8</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="6" t="n">
         <v>50.4</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="6" t="n">
         <v>33.2</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="P27" s="6" t="n">
         <v>38.3</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="R27" s="6" t="n">
         <v>26.7</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="T27" s="6" t="n">
         <v>-16.3</v>
       </c>
       <c r="U27" t="n">
@@ -5285,55 +5329,55 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="6" t="n">
         <v>5.6</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="6" t="n">
         <v>6.7</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="6" t="n">
         <v>16.5</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="6" t="n">
         <v>30.9</v>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" s="6" t="n">
         <v>21.4</v>
       </c>
       <c r="K28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="6" t="n">
         <v>49</v>
       </c>
       <c r="M28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="6" t="n">
         <v>27.2</v>
       </c>
       <c r="O28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="P28" s="6" t="n">
         <v>13.7</v>
       </c>
       <c r="Q28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="4" t="n">
+      <c r="R28" s="6" t="n">
         <v>22.6</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="4" t="n">
+      <c r="T28" s="6" t="n">
         <v>-3.6</v>
       </c>
       <c r="U28" t="n">
@@ -5356,55 +5400,55 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="6" t="n">
         <v>5.8</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="6" t="n">
         <v>-7.7</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="6" t="n">
         <v>-0.2</v>
       </c>
       <c r="I29" t="n">
         <v>16</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J29" s="6" t="n">
         <v>41.6</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="6" t="n">
         <v>13.9</v>
       </c>
       <c r="M29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N29" s="6" t="n">
         <v>23.6</v>
       </c>
       <c r="O29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="P29" s="6" t="n">
         <v>4.4</v>
       </c>
       <c r="Q29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="R29" s="6" t="n">
         <v>6.8</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="T29" s="6" t="n">
         <v>-13.3</v>
       </c>
       <c r="U29" t="n">
@@ -5427,55 +5471,55 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="6" t="n">
         <v>-1</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="6" t="n">
         <v>4.9</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="6" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="6" t="n">
         <v>-1.1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="J30" s="6" t="n">
         <v>32.8</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="6" t="n">
         <v>24.8</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="6" t="n">
         <v>-11.9</v>
       </c>
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="P30" s="6" t="n">
         <v>-14.4</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="4" t="n">
+      <c r="R30" s="6" t="n">
         <v>-13.5</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="T30" s="6" t="n">
         <v>-1.2</v>
       </c>
       <c r="U30" t="n">
@@ -5498,55 +5542,55 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="6" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="6" t="n">
         <v>-6</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="6" t="n">
         <v>-6.3</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" s="6" t="n">
         <v>26.2</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="6" t="n">
         <v>32.1</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="6" t="n">
         <v>-12.8</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="P31" s="6" t="n">
         <v>-17.8</v>
       </c>
       <c r="Q31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="R31" s="6" t="n">
         <v>-23.6</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="T31" s="6" t="n">
         <v>-2</v>
       </c>
       <c r="U31" t="n">
@@ -5569,55 +5613,55 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="6" t="n">
         <v>-3</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="6" t="n">
         <v>-7.5</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="6" t="n">
         <v>-15</v>
       </c>
       <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="J32" s="6" t="n">
         <v>22.7</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="L32" s="6" t="n">
         <v>18.9</v>
       </c>
       <c r="M32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="6" t="n">
         <v>-9.300000000000001</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="P32" s="6" t="n">
         <v>-27.4</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="4" t="n">
+      <c r="R32" s="6" t="n">
         <v>-32.9</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="4" t="inlineStr"/>
+      <c r="T32" s="6" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5636,55 +5680,55 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="6" t="n">
         <v>-6.5</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="6" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="6" t="n">
         <v>39.3</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="6" t="n">
         <v>57.4</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="6" t="n">
         <v>45</v>
       </c>
       <c r="K33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="L33" s="6" t="n">
         <v>25.6</v>
       </c>
       <c r="M33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="6" t="n">
         <v>-2.4</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="P33" s="6" t="n">
         <v>-36.6</v>
       </c>
       <c r="Q33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="4" t="n">
+      <c r="R33" s="6" t="n">
         <v>23.8</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="T33" s="6" t="n">
         <v>46.2</v>
       </c>
       <c r="U33" t="n">
@@ -5707,55 +5751,55 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="6" t="n">
         <v>-2</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="6" t="n">
         <v>-7.1</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="6" t="n">
         <v>-12.2</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="6" t="n">
         <v>19.6</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="6" t="n">
         <v>36.7</v>
       </c>
       <c r="I34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="J34" s="6" t="n">
         <v>52.1</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="6" t="n">
         <v>12</v>
       </c>
       <c r="M34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="O34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="P34" s="6" t="n">
         <v>-34</v>
       </c>
       <c r="Q34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="R34" s="6" t="n">
         <v>-2.8</v>
       </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="T34" s="6" t="n">
         <v>44</v>
       </c>
       <c r="U34" t="n">
@@ -5778,55 +5822,55 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="6" t="n">
         <v>-4.2</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="6" t="n">
         <v>-11.5</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="6" t="n">
         <v>-20.9</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="6" t="n">
         <v>8.6</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="6" t="n">
         <v>39.8</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J35" s="6" t="n">
         <v>99.7</v>
       </c>
       <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="6" t="n">
         <v>24.2</v>
       </c>
       <c r="M35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="6" t="n">
         <v>16.3</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="4" t="n">
+      <c r="P35" s="6" t="n">
         <v>-37.8</v>
       </c>
       <c r="Q35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="4" t="n">
+      <c r="R35" s="6" t="n">
         <v>6.8</v>
       </c>
       <c r="S35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="T35" s="6" t="n">
         <v>19.3</v>
       </c>
       <c r="U35" t="n">
@@ -5849,55 +5893,55 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="6" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="6" t="n">
         <v>-4.3</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="6" t="n">
         <v>-17.5</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="6" t="n">
         <v>-22.9</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="6" t="n">
         <v>-17</v>
       </c>
       <c r="I36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="J36" s="6" t="n">
         <v>56.6</v>
       </c>
       <c r="K36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="L36" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="M36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="6" t="n">
         <v>-29</v>
       </c>
       <c r="O36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="P36" s="6" t="n">
         <v>-28.9</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="4" t="n">
+      <c r="R36" s="6" t="n">
         <v>41.9</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="4" t="inlineStr"/>
+      <c r="T36" s="6" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -5916,55 +5960,55 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="6" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="6" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="6" t="n">
         <v>-13.5</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="6" t="n">
         <v>-24</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="6" t="n">
         <v>-21.1</v>
       </c>
       <c r="I37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="6" t="n">
         <v>31.8</v>
       </c>
       <c r="K37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="L37" s="6" t="n">
         <v>8.5</v>
       </c>
       <c r="M37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="6" t="n">
         <v>-10.8</v>
       </c>
       <c r="O37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="P37" s="6" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="4" t="n">
+      <c r="R37" s="6" t="n">
         <v>13.1</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="T37" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="U37" t="n">
@@ -5987,55 +6031,55 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="6" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="6" t="n">
         <v>-17.8</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="6" t="n">
         <v>-24.5</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="6" t="n">
         <v>-14.8</v>
       </c>
       <c r="I38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="J38" s="6" t="n">
         <v>27.1</v>
       </c>
       <c r="K38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="L38" s="6" t="n">
         <v>-14.9</v>
       </c>
       <c r="M38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="6" t="n">
         <v>-35.2</v>
       </c>
       <c r="O38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="P38" s="6" t="n">
         <v>-19.7</v>
       </c>
       <c r="Q38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="4" t="n">
+      <c r="R38" s="6" t="n">
         <v>50.7</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="4" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -6054,55 +6098,55 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="6" t="n">
         <v>3.4</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="6" t="n">
         <v>7.8</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="6" t="n">
         <v>-11.2</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="6" t="n">
         <v>-19.8</v>
       </c>
       <c r="I39" t="n">
         <v>11</v>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="6" t="n">
         <v>-13</v>
       </c>
       <c r="K39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="6" t="n">
         <v>-11</v>
       </c>
       <c r="M39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="6" t="n">
         <v>-18.6</v>
       </c>
       <c r="O39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="P39" s="6" t="n">
         <v>-11.9</v>
       </c>
       <c r="Q39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="4" t="n">
+      <c r="R39" s="6" t="n">
         <v>-3</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="T39" s="6" t="n">
         <v>302.8</v>
       </c>
       <c r="U39" t="n">
@@ -6125,55 +6169,55 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="6" t="n">
         <v>2.7</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="6" t="n">
         <v>-2.9</v>
       </c>
       <c r="I40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="J40" s="6" t="n">
         <v>10.8</v>
       </c>
       <c r="K40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="L40" s="6" t="n">
         <v>42.6</v>
       </c>
       <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="6" t="n">
         <v>-3.3</v>
       </c>
       <c r="O40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="P40" s="6" t="n">
         <v>-4.8</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="4" t="n">
+      <c r="R40" s="6" t="n">
         <v>-1.2</v>
       </c>
       <c r="S40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="4" t="n">
+      <c r="T40" s="6" t="n">
         <v>1.2</v>
       </c>
       <c r="U40" t="n">
@@ -6196,55 +6240,55 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="6" t="n">
         <v>3.4</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="6" t="n">
         <v>1.7</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="6" t="n">
         <v>-10.5</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="6" t="n">
         <v>-18.9</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="6" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="I41" t="n">
         <v>7</v>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="J41" s="6" t="n">
         <v>101.1</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L41" s="6" t="n">
         <v>4.1</v>
       </c>
       <c r="M41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="N41" s="6" t="n">
         <v>-11.4</v>
       </c>
       <c r="O41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="P41" s="6" t="n">
         <v>-21.6</v>
       </c>
       <c r="Q41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="4" t="n">
+      <c r="R41" s="6" t="n">
         <v>33.2</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="4" t="n">
+      <c r="T41" s="6" t="n">
         <v>41.8</v>
       </c>
       <c r="U41" t="n">
@@ -6267,55 +6311,55 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="6" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="6" t="n">
         <v>-6.1</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="6" t="n">
         <v>-17.2</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="6" t="n">
         <v>-22.7</v>
       </c>
       <c r="I42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="J42" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="K42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="L42" s="6" t="n">
         <v>-0.5</v>
       </c>
       <c r="M42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="6" t="n">
         <v>-27</v>
       </c>
       <c r="O42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="P42" s="6" t="n">
         <v>-10.4</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="4" t="n">
+      <c r="R42" s="6" t="n">
         <v>-6.4</v>
       </c>
       <c r="S42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="T42" s="6" t="n">
         <v>-6.6</v>
       </c>
       <c r="U42" t="n">
@@ -6338,55 +6382,55 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="6" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="6" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="6" t="n">
         <v>-8</v>
       </c>
       <c r="I43" t="n">
         <v>6</v>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="J43" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="K43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="L43" s="6" t="n">
         <v>29.7</v>
       </c>
       <c r="M43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="N43" s="6" t="n">
         <v>3.8</v>
       </c>
       <c r="O43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="4" t="n">
+      <c r="P43" s="6" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="4" t="n">
+      <c r="R43" s="6" t="n">
         <v>-3.8</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="4" t="n">
+      <c r="T43" s="6" t="n">
         <v>17.5</v>
       </c>
       <c r="U43" t="n">
@@ -6409,55 +6453,55 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="6" t="n">
         <v>13.2</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="6" t="n">
         <v>3.3</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="6" t="n">
         <v>-0.3</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="J44" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="K44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="L44" s="6" t="n">
         <v>-12.2</v>
       </c>
       <c r="M44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="6" t="n">
         <v>-14</v>
       </c>
       <c r="O44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="4" t="n">
+      <c r="P44" s="6" t="n">
         <v>-24.5</v>
       </c>
       <c r="Q44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="4" t="n">
+      <c r="R44" s="6" t="n">
         <v>-15.7</v>
       </c>
       <c r="S44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="4" t="n">
+      <c r="T44" s="6" t="n">
         <v>58.4</v>
       </c>
       <c r="U44" t="n">
@@ -6480,55 +6524,55 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="6" t="n">
         <v>9.1</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="6" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="6" t="n">
         <v>-15.1</v>
       </c>
       <c r="I45" t="n">
         <v>9</v>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="J45" s="6" t="n">
         <v>-2.9</v>
       </c>
       <c r="K45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="L45" s="6" t="n">
         <v>-4.2</v>
       </c>
       <c r="M45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="6" t="n">
         <v>-18.3</v>
       </c>
       <c r="O45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="4" t="n">
+      <c r="P45" s="6" t="n">
         <v>-13.4</v>
       </c>
       <c r="Q45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="4" t="n">
+      <c r="R45" s="6" t="n">
         <v>-7.5</v>
       </c>
       <c r="S45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="4" t="n">
+      <c r="T45" s="6" t="n">
         <v>72.7</v>
       </c>
       <c r="U45" t="n">
@@ -6771,12 +6815,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6819,15 +6863,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>Cursor AI 인수 희석+8/6 락업만료(9억주) 매도압력 -6.7%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6870,15 +6918,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>실적 상회에도 $14억 인수 발표 불안 -4.2%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6919,15 +6971,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>AI 광고기술 경쟁심화 우려, 섹터 수급 부진</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6968,15 +7024,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>7/29 실적 앞두고 이익감소 전망·HVAC 수요둔화 우려</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7021,15 +7081,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>매출 상회에도 수술건수 둔화(12% YoY)·ACA 축소 우려</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7074,15 +7138,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7123,10 +7187,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7174,15 +7238,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7225,15 +7289,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>Plozasiran 3상서 중성지방 79~81% 감소 호성적 발표 +19%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7274,15 +7342,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>2Q EPS $2.76(예상 상회)+FY26 가이던스 상향 +10%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7327,15 +7399,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>BofA·바클레이즈 등 목표가 일제 상향, 호실적 기대</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7376,15 +7452,19 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>독일 EnBW 등과 신규 LNG 판매계약 확대</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7425,15 +7505,19 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>WAB 호실적 halo+실적 기대(단독 촉매 미확인)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7474,15 +7558,15 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7523,15 +7607,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7576,15 +7660,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7623,15 +7707,15 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="6" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7670,15 +7754,15 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7723,15 +7807,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7776,15 +7860,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7829,15 +7913,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7882,15 +7966,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7935,15 +8019,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7984,15 +8068,15 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="6" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8037,15 +8121,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8090,15 +8174,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8143,15 +8227,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8196,10 +8280,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8249,14 +8333,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>(전일) General Mills·월마트 재생농업 제휴 발표+BMO 목표가 상향</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8302,14 +8386,14 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>(전일) AES(글로벌 발전·재생에너지 유틸리티): 7/15 분기배당 선언+재생에너지 확장, 7/30 실적 기대</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8357,10 +8441,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8410,14 +8494,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>(전일) 정제 업황 호조, Raymond James TP $235 상향·정유 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8467,10 +8551,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8520,10 +8604,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8573,10 +8657,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M36" s="6" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8626,10 +8710,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="6" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8679,14 +8763,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>(전일) 정제마진 강세 지속, 애널리스트 목표가 상향 랠리</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8736,10 +8820,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8789,10 +8873,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="6" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8842,7 +8926,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M41"/>
@@ -8942,12 +9026,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8992,15 +9076,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>금리상승·엔약세 수혜 금융 로테이션, 은행주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9045,15 +9133,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>금리상승 수혜 메가뱅크 강세, 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9098,15 +9190,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>금융 로테이션 동반 신탁은행 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9151,15 +9247,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>금리·운용수익 개선 기대 손보 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9204,10 +9304,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>금융 로테이션 속 리스·금융 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9253,10 +9357,10 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9306,10 +9410,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9355,14 +9459,14 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>(전일) 캐논(카메라·사무기기·반도체 노광): 광범위 자율반등+7/27 결산 앞둔 매수</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9408,7 +9512,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>(전일) 닛폰스틸(일본 최대 철강): US스틸 철강가 호조·FY27 이익 1000억엔 기여 기대로 자율반등</t>
         </is>
@@ -9512,12 +9616,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9558,15 +9662,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>경기민감 항공, 여객수요 회복 기대 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9607,15 +9715,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>통신 방어주로 테크 약세장서 상대 강세</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9656,15 +9768,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>바이오테크 개별 강세(섹터 수급)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9709,10 +9825,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>금리·배당 매력 금융, HSBC 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9762,7 +9882,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>(전일) SITC(아시아 역내 컨테이너 해운): 컨테이너 운임 4년래 고점·중동 리스크로 역내 운임 반등 수혜</t>
         </is>
@@ -9866,12 +9986,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9916,15 +10036,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>데이터센터 400G 스위치 수요+상반기 순익 +33~66% 예증, AI네트워킹 주도 +13.7%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9967,15 +10091,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>이더넷 스위치칩 AI수혜 테마, 반도체 섹터 강세 동반 +8.9%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10016,15 +10144,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>상반기 순익 +114~130% 예증(구리·금 강세 수혜) +7.8%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10069,15 +10201,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>AI서버 상반기 순익 +226~288% 예증 후 섹터 강세 유지</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10122,10 +10258,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>미 상무부 램리서치·AMAT·KLA에 화홍향 장비 출하중단 지시 -1.9%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10175,7 +10315,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>(전일) 쯔광구펀(H3C 서버·네트워크장비): AI연산 수요·H3C 매출급증+상반기 순이익 83~123% 증가 예고로 연속 상한가</t>
         </is>

--- a/신고신저가_20260723.xlsx
+++ b/신고신저가_20260723.xlsx
@@ -8,19 +8,20 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터동향" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터ETF" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미국" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일본" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="홍콩" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="중국A" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주요지수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터동향" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터ETF" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미국" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일본" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="홍콩" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="중국A" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'섹터동향'!$A$1:$I$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'미국'!$A$1:$M$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'일본'!$A$1:$M$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'홍콩'!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'중국A'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'섹터동향'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미국'!$A$1:$M$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'홍콩'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'중국A'!$A$1:$M$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,8 +29,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -44,10 +46,10 @@
     </font>
     <font/>
     <font>
-      <color rgb="00C00000"/>
+      <color rgb="000000C0"/>
     </font>
     <font>
-      <color rgb="000000C0"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -75,14 +77,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -668,6 +672,388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>지수</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>지수레벨</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1주</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>52주위치%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S&amp;P500</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7498.96</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>92</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>나스닥종합</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25690.9</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="I3" t="n">
+        <v>78</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7045.48</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>67.19</v>
+      </c>
+      <c r="I4" t="n">
+        <v>65</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>닛케이225</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>66463.59</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="I5" t="n">
+        <v>82</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>상해종합</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3867.03</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="I6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CSI300</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4717.24</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I7" t="n">
+        <v>66</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>홍콩</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>항셍</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24892.66</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="I8" t="n">
+        <v>42</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>홍콩</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>항셍테크</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4668.23</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>-7.85</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>-15.37</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -752,7 +1138,7 @@
       <c r="F2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -787,7 +1173,7 @@
       <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -822,7 +1208,7 @@
       <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -857,7 +1243,7 @@
       <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -892,7 +1278,7 @@
       <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -927,7 +1313,7 @@
       <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -962,7 +1348,7 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -997,7 +1383,7 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1032,7 +1418,7 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1067,7 +1453,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1102,7 +1488,7 @@
       <c r="F12" t="n">
         <v>-1</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1137,7 +1523,7 @@
       <c r="F13" t="n">
         <v>-1</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1172,7 +1558,7 @@
       <c r="F14" t="n">
         <v>-1</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1452,7 +1838,7 @@
       <c r="F22" t="n">
         <v>7</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1487,7 +1873,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1522,7 +1908,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2082,7 +2468,7 @@
       <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2117,7 +2503,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2152,7 +2538,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2187,7 +2573,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2712,7 +3098,7 @@
       <c r="F58" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2747,7 +3133,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2782,7 +3168,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3328,7 +3714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3483,55 +3869,55 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="8" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="8" t="n">
         <v>-6.2</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J2" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="L2" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="N2" s="8" t="n">
         <v>56</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="P2" s="8" t="n">
         <v>-27.7</v>
       </c>
       <c r="Q2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="R2" s="8" t="n">
         <v>34.7</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="T2" s="8" t="n">
         <v>43.6</v>
       </c>
       <c r="U2" t="n">
@@ -3554,55 +3940,55 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="8" t="n">
         <v>6.2</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="I3" t="n">
         <v>8</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J3" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="L3" s="8" t="n">
         <v>2.5</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="N3" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="P3" s="8" t="n">
         <v>-2.1</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="R3" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="T3" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="U3" t="n">
@@ -3625,55 +4011,55 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="8" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="8" t="n">
         <v>4.4</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="8" t="n">
         <v>3.2</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="8" t="n">
         <v>30.6</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="8" t="n">
         <v>12</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="P4" s="8" t="n">
         <v>-10.6</v>
       </c>
       <c r="Q4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="R4" s="8" t="n">
         <v>34.8</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="T4" s="8" t="n">
         <v>-1.7</v>
       </c>
       <c r="U4" t="n">
@@ -3696,55 +4082,55 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="8" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="8" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="8" t="n">
         <v>-4</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="8" t="n">
         <v>-4.1</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="8" t="n">
         <v>7.4</v>
       </c>
       <c r="K5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="N5" s="8" t="n">
         <v>39.6</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="P5" s="8" t="n">
         <v>-36.3</v>
       </c>
       <c r="Q5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="R5" s="8" t="n">
         <v>27.9</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="T5" s="8" t="n">
         <v>29.6</v>
       </c>
       <c r="U5" t="n">
@@ -3767,55 +4153,55 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="8" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="8" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="8" t="n">
         <v>-6.7</v>
       </c>
       <c r="I6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="8" t="n">
         <v>34.7</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="8" t="n">
         <v>52.8</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="P6" s="8" t="n">
         <v>-37.6</v>
       </c>
       <c r="Q6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="R6" s="8" t="n">
         <v>16</v>
       </c>
       <c r="S6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="T6" s="8" t="n">
         <v>26.9</v>
       </c>
       <c r="U6" t="n">
@@ -3838,55 +4224,55 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="8" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="8" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="8" t="n">
         <v>4.6</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="P7" s="8" t="n">
         <v>-5.6</v>
       </c>
       <c r="Q7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="R7" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="T7" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="U7" t="n">
@@ -3909,55 +4295,55 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="8" t="n">
         <v>2.7</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="8" t="n">
         <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="K8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="N8" s="8" t="n">
         <v>-0.8</v>
       </c>
       <c r="O8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="P8" s="8" t="n">
         <v>-0.8</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="R8" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="T8" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="U8" t="n">
@@ -3980,55 +4366,55 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="8" t="n">
         <v>9.5</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="8" t="n">
         <v>6.7</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="8" t="n">
         <v>34.2</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="8" t="n">
         <v>7.9</v>
       </c>
       <c r="K9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="L9" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N9" s="8" t="n">
         <v>-0.6</v>
       </c>
       <c r="O9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="P9" s="8" t="n">
         <v>64.3</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="R9" s="8" t="n">
         <v>53.3</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="T9" s="8" t="n">
         <v>-32.7</v>
       </c>
       <c r="U9" t="n">
@@ -4051,55 +4437,55 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="8" t="n">
         <v>2.7</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="8" t="n">
         <v>2.8</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="8" t="n">
         <v>9</v>
       </c>
       <c r="I10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="8" t="n">
         <v>16</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="N10" s="8" t="n">
         <v>-7.2</v>
       </c>
       <c r="O10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="P10" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="R10" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="T10" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="U10" t="n">
@@ -4122,55 +4508,55 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="n">
         <v>1.4</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="8" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="8" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="8" t="n">
         <v>9.9</v>
       </c>
       <c r="K11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" s="8" t="n">
         <v>12.5</v>
       </c>
       <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="8" t="n">
         <v>-12.3</v>
       </c>
       <c r="Q11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="8" t="n">
         <v>27.4</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="U11" t="n">
@@ -4193,55 +4579,55 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="8" t="n">
         <v>3.7</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="8" t="n">
         <v>2.6</v>
       </c>
       <c r="K12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="8" t="n">
         <v>5.1</v>
       </c>
       <c r="M12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="P12" s="8" t="n">
         <v>-26.2</v>
       </c>
       <c r="Q12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="R12" s="8" t="n">
         <v>46.1</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="T12" s="8" t="n">
         <v>-2.2</v>
       </c>
       <c r="U12" t="n">
@@ -4264,55 +4650,55 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="8" t="n">
         <v>2.9</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="8" t="n">
         <v>7.4</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="I13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="K13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="N13" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="O13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="P13" s="8" t="n">
         <v>6.4</v>
       </c>
       <c r="Q13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="R13" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="S13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="T13" s="8" t="n">
         <v>-3.4</v>
       </c>
       <c r="U13" t="n">
@@ -4335,55 +4721,55 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="8" t="n">
         <v>7.1</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="8" t="n">
         <v>5.4</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="8" t="n">
         <v>-7.8</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="8" t="n">
         <v>15.6</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="8" t="n">
         <v>41.4</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" s="8" t="n">
         <v>37.2</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R14" s="8" t="n">
         <v>39.3</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="T14" s="8" t="n">
         <v>-29</v>
       </c>
       <c r="U14" t="n">
@@ -4406,55 +4792,55 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="8" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="8" t="n">
         <v>-5.8</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="8" t="n">
         <v>1.9</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="8" t="n">
         <v>42</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="M15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" s="8" t="n">
         <v>32</v>
       </c>
       <c r="O15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P15" s="8" t="n">
         <v>-2.4</v>
       </c>
       <c r="Q15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="R15" s="8" t="n">
         <v>12.6</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="T15" s="8" t="n">
         <v>-6.1</v>
       </c>
       <c r="U15" t="n">
@@ -4477,55 +4863,55 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="8" t="n">
         <v>-0</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="8" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="8" t="n">
         <v>7.4</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="K16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="M16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="O16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="P16" s="8" t="n">
         <v>-9.4</v>
       </c>
       <c r="Q16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="R16" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="S16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="U16" t="n">
@@ -4548,55 +4934,55 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="8" t="n">
         <v>3.2</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="8" t="n">
         <v>4.5</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="8" t="n">
         <v>-6.4</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="I17" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="M17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="O17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="P17" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="8" t="n">
         <v>-8.4</v>
       </c>
       <c r="S17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="T17" s="8" t="n">
         <v>4.6</v>
       </c>
       <c r="U17" t="n">
@@ -4619,55 +5005,55 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="8" t="n">
         <v>5.2</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="8" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="8" t="n">
         <v>-5.5</v>
       </c>
       <c r="I18" t="n">
         <v>17</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="K18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="M18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N18" s="8" t="n">
         <v>40.5</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="P18" s="8" t="n">
         <v>-10.7</v>
       </c>
       <c r="Q18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R18" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="T18" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="U18" t="n">
@@ -4690,55 +5076,55 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="8" t="n">
         <v>-29.2</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="8" t="n">
         <v>-12.3</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="8" t="n">
         <v>40</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="8" t="n">
         <v>68.8</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="M19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N19" s="8" t="n">
         <v>35</v>
       </c>
       <c r="O19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="P19" s="8" t="n">
         <v>16.1</v>
       </c>
       <c r="Q19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="R19" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="S19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="T19" s="8" t="n">
         <v>-8.6</v>
       </c>
       <c r="U19" t="n">
@@ -4761,55 +5147,55 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="8" t="n">
         <v>-0</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="8" t="n">
         <v>-6.1</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="8" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="8" t="n">
         <v>20</v>
       </c>
       <c r="I20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="8" t="n">
         <v>31.1</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="L20" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="M20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N20" s="8" t="n">
         <v>33.9</v>
       </c>
       <c r="O20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="P20" s="8" t="n">
         <v>-9.9</v>
       </c>
       <c r="Q20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="R20" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="T20" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="U20" t="n">
@@ -4832,55 +5218,55 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="8" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="8" t="n">
         <v>-11.3</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="8" t="n">
         <v>31.8</v>
       </c>
       <c r="I21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="8" t="n">
         <v>27.5</v>
       </c>
       <c r="K21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="M21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="8" t="n">
         <v>33.7</v>
       </c>
       <c r="O21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="P21" s="8" t="n">
         <v>-23</v>
       </c>
       <c r="Q21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="R21" s="8" t="n">
         <v>25</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="T21" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="U21" t="n">
@@ -4903,55 +5289,55 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="8" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="8" t="n">
         <v>9.5</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="8" t="n">
         <v>4.6</v>
       </c>
       <c r="I22" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="K22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L22" s="8" t="n">
         <v>21</v>
       </c>
       <c r="M22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N22" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="O22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="P22" s="8" t="n">
         <v>-5.9</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="R22" s="8" t="n">
         <v>3.5</v>
       </c>
       <c r="S22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="T22" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="U22" t="n">
@@ -4974,55 +5360,55 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="8" t="n">
         <v>1.8</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="8" t="n">
         <v>-7.6</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="8" t="n">
         <v>1.9</v>
       </c>
       <c r="I23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="8" t="n">
         <v>37.4</v>
       </c>
       <c r="K23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="L23" s="8" t="n">
         <v>6.3</v>
       </c>
       <c r="M23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" s="8" t="n">
         <v>35</v>
       </c>
       <c r="O23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="P23" s="8" t="n">
         <v>13.2</v>
       </c>
       <c r="Q23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="R23" s="8" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="S23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="T23" s="8" t="n">
         <v>-10.7</v>
       </c>
       <c r="U23" t="n">
@@ -5045,55 +5431,55 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="8" t="n">
         <v>4.7</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="8" t="n">
         <v>3.2</v>
       </c>
       <c r="I24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="K24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="L24" s="8" t="n">
         <v>-0</v>
       </c>
       <c r="M24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="N24" s="8" t="n">
         <v>19</v>
       </c>
       <c r="O24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="P24" s="8" t="n">
         <v>13.1</v>
       </c>
       <c r="Q24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="R24" s="8" t="n">
         <v>4.7</v>
       </c>
       <c r="S24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="T24" s="8" t="n">
         <v>-17.1</v>
       </c>
       <c r="U24" t="n">
@@ -5116,55 +5502,55 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="8" t="n">
         <v>6.4</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="8" t="n">
         <v>4.7</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="8" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="I25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="8" t="n">
         <v>41.5</v>
       </c>
       <c r="K25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="L25" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="M25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="8" t="n">
         <v>42</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="P25" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="R25" s="8" t="n">
         <v>29.2</v>
       </c>
       <c r="S25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="T25" s="8" t="n">
         <v>1.9</v>
       </c>
       <c r="U25" t="n">
@@ -5187,55 +5573,55 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="8" t="n">
         <v>4.1</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="8" t="n">
         <v>3.2</v>
       </c>
       <c r="I26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="K26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="L26" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="M26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="P26" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="Q26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="R26" s="8" t="n">
         <v>-4.4</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="T26" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="U26" t="n">
@@ -5258,55 +5644,55 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="8" t="n">
         <v>2.9</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="8" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="8" t="n">
         <v>44.8</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="L27" s="8" t="n">
         <v>50.4</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="8" t="n">
         <v>33.2</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="P27" s="8" t="n">
         <v>38.3</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="R27" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="T27" s="8" t="n">
         <v>-16.3</v>
       </c>
       <c r="U27" t="n">
@@ -5329,55 +5715,55 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="8" t="n">
         <v>6.7</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="8" t="n">
         <v>30.9</v>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="K28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="L28" s="8" t="n">
         <v>49</v>
       </c>
       <c r="M28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N28" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="O28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="P28" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="Q28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="R28" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="T28" s="8" t="n">
         <v>-3.6</v>
       </c>
       <c r="U28" t="n">
@@ -5400,55 +5786,55 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="8" t="n">
         <v>5.8</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="8" t="n">
         <v>-7.7</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="8" t="n">
         <v>-0.2</v>
       </c>
       <c r="I29" t="n">
         <v>16</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="8" t="n">
         <v>41.6</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="L29" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="M29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="N29" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="O29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="P29" s="8" t="n">
         <v>4.4</v>
       </c>
       <c r="Q29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="R29" s="8" t="n">
         <v>6.8</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="T29" s="8" t="n">
         <v>-13.3</v>
       </c>
       <c r="U29" t="n">
@@ -5471,55 +5857,55 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="n">
         <v>-1</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="8" t="n">
         <v>4.9</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="8" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="8" t="n">
         <v>-1.1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="8" t="n">
         <v>32.8</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="L30" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" s="8" t="n">
         <v>-11.9</v>
       </c>
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="P30" s="8" t="n">
         <v>-14.4</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="R30" s="8" t="n">
         <v>-13.5</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="T30" s="8" t="n">
         <v>-1.2</v>
       </c>
       <c r="U30" t="n">
@@ -5542,55 +5928,55 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="8" t="n">
         <v>4.6</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="8" t="n">
         <v>-6</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="8" t="n">
         <v>-6.3</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="L31" s="8" t="n">
         <v>32.1</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N31" s="8" t="n">
         <v>-12.8</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="P31" s="8" t="n">
         <v>-17.8</v>
       </c>
       <c r="Q31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="R31" s="8" t="n">
         <v>-23.6</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="T31" s="8" t="n">
         <v>-2</v>
       </c>
       <c r="U31" t="n">
@@ -5613,55 +5999,55 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="n">
         <v>-3</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="8" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="8" t="n">
         <v>2.6</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="8" t="n">
         <v>-7.5</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="8" t="n">
         <v>-15</v>
       </c>
       <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="L32" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="M32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="N32" s="8" t="n">
         <v>-9.300000000000001</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="P32" s="8" t="n">
         <v>-27.4</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="R32" s="8" t="n">
         <v>-32.9</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
+      <c r="T32" s="8" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5680,55 +6066,55 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="8" t="n">
         <v>-6.5</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="8" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="8" t="n">
         <v>39.3</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="8" t="n">
         <v>57.4</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="8" t="n">
         <v>45</v>
       </c>
       <c r="K33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="L33" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="M33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="8" t="n">
         <v>-2.4</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="P33" s="8" t="n">
         <v>-36.6</v>
       </c>
       <c r="Q33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="R33" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="T33" s="8" t="n">
         <v>46.2</v>
       </c>
       <c r="U33" t="n">
@@ -5751,55 +6137,55 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="n">
         <v>-2</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="8" t="n">
         <v>-7.1</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="8" t="n">
         <v>-12.2</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="8" t="n">
         <v>36.7</v>
       </c>
       <c r="I34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="8" t="n">
         <v>52.1</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="L34" s="8" t="n">
         <v>12</v>
       </c>
       <c r="M34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="N34" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="O34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="P34" s="8" t="n">
         <v>-34</v>
       </c>
       <c r="Q34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="R34" s="8" t="n">
         <v>-2.8</v>
       </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="T34" s="8" t="n">
         <v>44</v>
       </c>
       <c r="U34" t="n">
@@ -5822,55 +6208,55 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="n">
         <v>-4.2</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="8" t="n">
         <v>-11.5</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="8" t="n">
         <v>-20.9</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="8" t="n">
         <v>39.8</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="8" t="n">
         <v>99.7</v>
       </c>
       <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="L35" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="M35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="8" t="n">
         <v>16.3</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="P35" s="8" t="n">
         <v>-37.8</v>
       </c>
       <c r="Q35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="R35" s="8" t="n">
         <v>6.8</v>
       </c>
       <c r="S35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="T35" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="U35" t="n">
@@ -5893,55 +6279,55 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="8" t="n">
         <v>-4.3</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="8" t="n">
         <v>-17.5</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="8" t="n">
         <v>-22.9</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="8" t="n">
         <v>-17</v>
       </c>
       <c r="I36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="8" t="n">
         <v>56.6</v>
       </c>
       <c r="K36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="L36" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="M36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" s="8" t="n">
         <v>-29</v>
       </c>
       <c r="O36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="P36" s="8" t="n">
         <v>-28.9</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="R36" s="8" t="n">
         <v>41.9</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
+      <c r="T36" s="8" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -5960,55 +6346,55 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="8" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="8" t="n">
         <v>-13.5</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="8" t="n">
         <v>-24</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="8" t="n">
         <v>-21.1</v>
       </c>
       <c r="I37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="8" t="n">
         <v>31.8</v>
       </c>
       <c r="K37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="L37" s="8" t="n">
         <v>8.5</v>
       </c>
       <c r="M37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" s="8" t="n">
         <v>-10.8</v>
       </c>
       <c r="O37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="P37" s="8" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="R37" s="8" t="n">
         <v>13.1</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="T37" s="8" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="U37" t="n">
@@ -6031,55 +6417,55 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="8" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="8" t="n">
         <v>-17.8</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="8" t="n">
         <v>-24.5</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" s="8" t="n">
         <v>-14.8</v>
       </c>
       <c r="I38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="8" t="n">
         <v>27.1</v>
       </c>
       <c r="K38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="L38" s="8" t="n">
         <v>-14.9</v>
       </c>
       <c r="M38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="N38" s="8" t="n">
         <v>-35.2</v>
       </c>
       <c r="O38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="P38" s="8" t="n">
         <v>-19.7</v>
       </c>
       <c r="Q38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="R38" s="8" t="n">
         <v>50.7</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
+      <c r="T38" s="8" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -6098,55 +6484,55 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="8" t="n">
         <v>7.8</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="8" t="n">
         <v>-11.2</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="8" t="n">
         <v>-19.8</v>
       </c>
       <c r="I39" t="n">
         <v>11</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="J39" s="8" t="n">
         <v>-13</v>
       </c>
       <c r="K39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="L39" s="8" t="n">
         <v>-11</v>
       </c>
       <c r="M39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="8" t="n">
         <v>-18.6</v>
       </c>
       <c r="O39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="P39" s="8" t="n">
         <v>-11.9</v>
       </c>
       <c r="Q39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="R39" s="8" t="n">
         <v>-3</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="T39" s="8" t="n">
         <v>302.8</v>
       </c>
       <c r="U39" t="n">
@@ -6169,55 +6555,55 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="8" t="n">
         <v>2.7</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="8" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H40" s="8" t="n">
         <v>-2.9</v>
       </c>
       <c r="I40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J40" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="K40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="L40" s="8" t="n">
         <v>42.6</v>
       </c>
       <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" s="8" t="n">
         <v>-3.3</v>
       </c>
       <c r="O40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="P40" s="8" t="n">
         <v>-4.8</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="R40" s="8" t="n">
         <v>-1.2</v>
       </c>
       <c r="S40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="T40" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="U40" t="n">
@@ -6240,55 +6626,55 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="8" t="n">
         <v>-10.5</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G41" s="8" t="n">
         <v>-18.9</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="H41" s="8" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="I41" t="n">
         <v>7</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="J41" s="8" t="n">
         <v>101.1</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="L41" s="8" t="n">
         <v>4.1</v>
       </c>
       <c r="M41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" s="8" t="n">
         <v>-11.4</v>
       </c>
       <c r="O41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="P41" s="8" t="n">
         <v>-21.6</v>
       </c>
       <c r="Q41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="R41" s="8" t="n">
         <v>33.2</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="T41" s="8" t="n">
         <v>41.8</v>
       </c>
       <c r="U41" t="n">
@@ -6311,55 +6697,55 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="8" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="8" t="n">
         <v>-6.1</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G42" s="8" t="n">
         <v>-17.2</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H42" s="8" t="n">
         <v>-22.7</v>
       </c>
       <c r="I42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J42" s="8" t="n">
         <v>2.5</v>
       </c>
       <c r="K42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="L42" s="8" t="n">
         <v>-0.5</v>
       </c>
       <c r="M42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="N42" s="8" t="n">
         <v>-27</v>
       </c>
       <c r="O42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="P42" s="8" t="n">
         <v>-10.4</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="R42" s="8" t="n">
         <v>-6.4</v>
       </c>
       <c r="S42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="T42" s="8" t="n">
         <v>-6.6</v>
       </c>
       <c r="U42" t="n">
@@ -6382,55 +6768,55 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="8" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="8" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="8" t="n">
         <v>3.6</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" s="8" t="n">
         <v>-8</v>
       </c>
       <c r="I43" t="n">
         <v>6</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="8" t="n">
         <v>3.5</v>
       </c>
       <c r="K43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="L43" s="8" t="n">
         <v>29.7</v>
       </c>
       <c r="M43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="N43" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="O43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="P43" s="8" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="R43" s="8" t="n">
         <v>-3.8</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="T43" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="U43" t="n">
@@ -6453,55 +6839,55 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="8" t="n">
         <v>3.3</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" s="8" t="n">
         <v>-0.3</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" s="8" t="n">
         <v>4.7</v>
       </c>
       <c r="K44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="L44" s="8" t="n">
         <v>-12.2</v>
       </c>
       <c r="M44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="N44" s="8" t="n">
         <v>-14</v>
       </c>
       <c r="O44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="P44" s="8" t="n">
         <v>-24.5</v>
       </c>
       <c r="Q44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="R44" s="8" t="n">
         <v>-15.7</v>
       </c>
       <c r="S44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="T44" s="8" t="n">
         <v>58.4</v>
       </c>
       <c r="U44" t="n">
@@ -6524,55 +6910,55 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="8" t="n">
         <v>2.6</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" s="8" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H45" s="8" t="n">
         <v>-15.1</v>
       </c>
       <c r="I45" t="n">
         <v>9</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" s="8" t="n">
         <v>-2.9</v>
       </c>
       <c r="K45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="L45" s="8" t="n">
         <v>-4.2</v>
       </c>
       <c r="M45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="N45" s="8" t="n">
         <v>-18.3</v>
       </c>
       <c r="O45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="P45" s="8" t="n">
         <v>-13.4</v>
       </c>
       <c r="Q45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="R45" s="8" t="n">
         <v>-7.5</v>
       </c>
       <c r="S45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="T45" s="8" t="n">
         <v>72.7</v>
       </c>
       <c r="U45" t="n">
@@ -6723,7 +7109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6815,7 +7201,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6863,14 +7249,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>Cursor AI 인수 희석+8/6 락업만료(9억주) 매도압력 -6.7%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6918,14 +7304,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>실적 상회에도 $14억 인수 발표 불안 -4.2%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6971,14 +7357,14 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>AI 광고기술 경쟁심화 우려, 섹터 수급 부진</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7024,14 +7410,14 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>7/29 실적 앞두고 이익감소 전망·HVAC 수요둔화 우려</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7081,14 +7467,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>매출 상회에도 수술건수 둔화(12% YoY)·ACA 축소 우려</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7138,10 +7524,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7187,10 +7573,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7238,10 +7624,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="M9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7289,14 +7675,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>Plozasiran 3상서 중성지방 79~81% 감소 호성적 발표 +19%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7342,14 +7728,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>2Q EPS $2.76(예상 상회)+FY26 가이던스 상향 +10%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7399,14 +7785,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>BofA·바클레이즈 등 목표가 일제 상향, 호실적 기대</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7452,14 +7838,14 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>독일 EnBW 등과 신규 LNG 판매계약 확대</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7505,14 +7891,14 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>WAB 호실적 halo+실적 기대(단독 촉매 미확인)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7558,10 +7944,10 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr"/>
+      <c r="M15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7607,10 +7993,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7660,10 +8046,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr"/>
+      <c r="M17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7707,10 +8093,10 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="7" t="inlineStr"/>
+      <c r="M18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7754,10 +8140,10 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="7" t="inlineStr"/>
+      <c r="M19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7807,10 +8193,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7860,10 +8246,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
+      <c r="M21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7913,10 +8299,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7966,10 +8352,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
+      <c r="M23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8019,10 +8405,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
+      <c r="M24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8068,10 +8454,10 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="7" t="inlineStr"/>
+      <c r="M25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8121,10 +8507,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8174,10 +8560,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8227,10 +8613,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr"/>
+      <c r="M28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8280,10 +8666,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
+      <c r="M29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8333,14 +8719,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>(전일) General Mills·월마트 재생농업 제휴 발표+BMO 목표가 상향</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8386,14 +8772,14 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>(전일) AES(글로벌 발전·재생에너지 유틸리티): 7/15 분기배당 선언+재생에너지 확장, 7/30 실적 기대</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8441,10 +8827,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8494,14 +8880,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>(전일) 정제 업황 호조, Raymond James TP $235 상향·정유 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8551,10 +8937,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
+      <c r="M34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8604,10 +8990,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
+      <c r="M35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8657,10 +9043,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
+      <c r="M36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8710,10 +9096,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
+      <c r="M37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8763,14 +9149,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr">
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>(전일) 정제마진 강세 지속, 애널리스트 목표가 상향 랠리</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8820,10 +9206,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
+      <c r="M39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8873,10 +9259,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
+      <c r="M40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8926,7 +9312,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
+      <c r="M41" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M41"/>
@@ -8934,7 +9320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9026,7 +9412,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9076,14 +9462,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>금리상승·엔약세 수혜 금융 로테이션, 은행주 신고가</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9133,14 +9519,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>금리상승 수혜 메가뱅크 강세, 신고가</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9190,14 +9576,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>금융 로테이션 동반 신탁은행 신고가</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9247,14 +9633,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>금리·운용수익 개선 기대 손보 신고가</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9304,14 +9690,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>금융 로테이션 속 리스·금융 신고가</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9357,10 +9743,10 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9410,10 +9796,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9459,14 +9845,14 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>(전일) 캐논(카메라·사무기기·반도체 노광): 광범위 자율반등+7/27 결산 앞둔 매수</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9512,7 +9898,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>(전일) 닛폰스틸(일본 최대 철강): US스틸 철강가 호조·FY27 이익 1000억엔 기여 기대로 자율반등</t>
         </is>
@@ -9524,7 +9910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9616,7 +10002,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9662,14 +10048,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>경기민감 항공, 여객수요 회복 기대 신고가</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9715,14 +10101,14 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>통신 방어주로 테크 약세장서 상대 강세</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9768,14 +10154,14 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>바이오테크 개별 강세(섹터 수급)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9825,14 +10211,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>금리·배당 매력 금융, HSBC 신고가</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9882,7 +10268,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>(전일) SITC(아시아 역내 컨테이너 해운): 컨테이너 운임 4년래 고점·중동 리스크로 역내 운임 반등 수혜</t>
         </is>
@@ -9894,7 +10280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9986,7 +10372,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10036,14 +10422,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>데이터센터 400G 스위치 수요+상반기 순익 +33~66% 예증, AI네트워킹 주도 +13.7%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10091,14 +10477,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>이더넷 스위치칩 AI수혜 테마, 반도체 섹터 강세 동반 +8.9%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10144,14 +10530,14 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>상반기 순익 +114~130% 예증(구리·금 강세 수혜) +7.8%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10201,14 +10587,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>AI서버 상반기 순익 +226~288% 예증 후 섹터 강세 유지</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10258,14 +10644,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>미 상무부 램리서치·AMAT·KLA에 화홍향 장비 출하중단 지시 -1.9%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10315,7 +10701,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>(전일) 쯔광구펀(H3C 서버·네트워크장비): AI연산 수요·H3C 매출급증+상반기 순이익 83~123% 증가 예고로 연속 상한가</t>
         </is>

--- a/신고신저가_20260723.xlsx
+++ b/신고신저가_20260723.xlsx
@@ -10703,7 +10703,7 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>(전일) 쯔광구펀(H3C 서버·네트워크장비): AI연산 수요·H3C 매출급증+상반기 순이익 83~123% 증가 예고로 연속 상한가</t>
+          <t>상반기 순이익 최대 +123% 실적예고·AI서버 수주·紫光 지분정합 완료로 연속 상한가</t>
         </is>
       </c>
     </row>

--- a/신고신저가_20260723.xlsx
+++ b/신고신저가_20260723.xlsx
@@ -77,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,6 +86,9 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -615,42 +618,42 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 ■ 결론: 지난주 AI반도체 급락이 미국·중국서 하루 만에 반등 — SMCI 대규모 수주가 트리거로 미 반도체 랠리(SOX +5.2%), 중국A 신저 41→0 급반전. 단 온기가 일본·홍콩엔 미전달, 미·이란 지정학이 금·엔·유가로 번지는 중.</t>
+          <t>💬 ■ 결론: 7/22 글로벌 밸류·시클리컬 로테이션, 성장·테크 소프트. 미 금융·에너지·유틸이 신고가 주도, 일본 은행 랠리(장기금리 29년래 고), 중국A는 AI연산·유색금속만 선별 강세.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ 美: S&amp;P +0.9%·나스닥 +1.3% 반등(SMCI 수주 600억달러+SpaceX AI데이터센터) — 신고 32 vs 신저 8. 강세: 금융 순증 +8·에너지 +5·유틸 +4. ARWR 임상 호성적 +19%, WAB 실적상회 +10%. 약세: TE커넥티비티 인수우려 -4%.</t>
+          <t>■ 美: 지수 혼조(다우 -0.01%·S&amp;P -0.14%·나스닥 -0.57%) 속 신고 32(NEW20)/신저 8. 강세 금융(순강도+8, 중앙 PER 18.7)·에너지(+5)·유틸(XLU +2.2%)·소재. 약세 전자기술·기술서비스(각 -1). 애로우헤드파마 +19%(고중성지방혈증 3상 성공), 왑텍 +10%·펜스키 +9.9%·파카 +3.9%(운송·상용차 실적·Class8 수주 급증); 반면 AppLovin -3.8%·인튜이티브서지컬 -2.7%·TE커넥티비티 -4.2% 조정.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ 日: 닛케이 -0.17% 도지 — 오전 +1,200엔 급등분을 엔약세(163엔, 39년래 최저)·유가로 오후 전량 반납. 신고 9개 전부 금융(SMFG·재팬포스트뱅크·MS&amp;AD) — 금리·엔약세 수혜 로테이션.</t>
+          <t>■ 日: 은행 랠리. 신고 9(NEW5) 전부 금융(순강도+7, PER 16.6), 은행 ETF +2.2%. 장기금리 ~29년래 고수준(이자마진 확대 기대), 미쓰이스미토모FG(도카이도쿄 목표가 5830→8140엔 상향)·유초은행·오릭스 신고가.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ 홍콩: 항셍 -0.95%·항셍테크 -2~3% — 미 반도체 랠리 온기 미전달, 滔搏 -24% 심리 압박. 신고는 캐세이·HSBC 등 경기민감·금융뿐.</t>
+          <t>■ 홍콩: 지수 약세(2800 -1.0%·항셍테크 -3.0%)에도 밸류주 선별 신고 5(NEW4). 캐세이퍼시픽 +2.6%(상반기 순익 +62~76% 예고), HSBC +1.5%(JP모건 투자의견 상향), HKT·비원메디슨. 운송·통신·금융 강세.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ 中: 상해 +0.5% — 자사주매입·기관 자기매수 재개가 지지, 신저 0 급반전. 반도체·네트워킹 주도(루이지에 +13.7%), 단 화홍은 미 수출통제로 -1.9%.</t>
+          <t>■ 中: AI연산·유색금속만 강세, 성장주 소프트. 신고 6(NEW5). 유색금속 ETF +3.4%·반도체 +0.7% vs 테크 -2.0%·5G -4.2%. 루이제네트워크 +13.7%(상한가, H1 순익 +33~66%·AI DC 스위치 수주 최고)·성커통신 +8.9%·인스퍼 +2.0%(AI서버), 시부광업 +7.8%(구리값 급등).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ 체크: ①오늘밤 미국 반도체 랠리 지속성 ②엔 163엔 개입 경계 ③금·유가(미·이란) 인플레 재점화.</t>
+          <t>■ 체크: ①미 실적시즌 성장주 vs 밸류 로테이션 지속 여부 ②일본 장기금리·은행주 과열 ③중국 AI연산 체인 상한가 연속성</t>
         </is>
       </c>
     </row>
@@ -3720,30 +3723,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3764,90 +3768,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -3869,58 +3878,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>테크 -0.3%. 전자기술·기술서비스 섹터 약세(순강도 -1), 나스닥 -0.57% 동반 성장주 조정</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="F2" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="G2" s="9" t="n">
         <v>-6.2</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="H2" s="9" t="n">
         <v>16.7</v>
       </c>
-      <c r="H2" s="8" t="n">
+      <c r="I2" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="8" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="8" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="8" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="8" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="8" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="8" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3940,58 +3954,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>헬스케어 -0.5%. 헬스테크 혼조(신고2/신저2), 인튜이티브서지컬 -2.7% 등 개별 악재</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="F3" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="G3" s="9" t="n">
         <v>6.2</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="H3" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="I3" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>8</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="8" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="8" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="8" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="8" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="8" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4011,58 +4030,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>금융 +0.0%(보합). 지수는 평온하나 금융 신고 9개로 브레드스 최강(순강도+8), 실적 기대 로테이션</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="G4" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="H4" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="I4" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="8" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4082,58 +4106,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>경기소비재 -0.7%. 소비서비스 약세, 성장·소비주 부진</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="G5" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="H5" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="I5" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="8" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4153,58 +4182,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>커뮤니케이션 -0.8%. 섹터 혼조 속 약세, 광고·미디어 소프트</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="G6" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="I6" s="9" t="n">
         <v>-6.7</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="8" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="8" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4224,58 +4258,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>산업재 +0.1%. 운송·상용차 강세(왑텍·파카·펜스키 신고가)로 지지</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="G7" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="H7" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="I7" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="8" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="8" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4295,58 +4334,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>필수소비재 +0.4%. 방어주 순환매 유입, 신고 2개 강세</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="G8" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="H8" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="I8" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="8" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4366,58 +4410,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>에너지 +1.2%. 에너지미네랄 순강도+5, 유가 강세로 섹터 상위</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="G9" s="9" t="n">
         <v>9.5</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="H9" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="I9" s="9" t="n">
         <v>34.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="8" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="8" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="8" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="8" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="8" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="8" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4437,58 +4486,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>유틸리티 +2.2%(1D 최강). 금리 로테이션·방어 수요, 신고 4개 강세</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="F10" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="G10" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="H10" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="I10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="8" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="8" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4508,58 +4562,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>소재 +1.4%. Process Industries 강세, 시클리컬 로테이션 수혜</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="F11" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="G11" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="H11" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="I11" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="8" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="8" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="8" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4579,58 +4638,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>리츠 -0.4%. 소폭 약세, 방향성 제한</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="F12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="G12" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="H12" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="8" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="8" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="8" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="8" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4650,58 +4714,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="G13" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="H13" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="I13" s="9" t="n">
         <v>16.7</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="8" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="8" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4721,58 +4786,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="F14" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="G14" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="H14" s="9" t="n">
         <v>-7.8</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="I14" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="8" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="8" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="8" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4792,58 +4858,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="F15" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="G15" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="H15" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="I15" s="9" t="n">
         <v>11.1</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="8" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="8" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="8" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4863,58 +4930,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="F16" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="G16" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="H16" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="I16" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="8" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="8" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="8" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="8" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="8" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="8" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4934,58 +5002,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="F17" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="G17" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="H17" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="I17" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="8" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="8" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="8" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5005,58 +5074,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="F18" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="G18" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="H18" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="I18" s="9" t="n">
         <v>-5.5</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>17</v>
       </c>
-      <c r="J18" s="8" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="8" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="8" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5076,58 +5146,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="F19" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="G19" s="9" t="n">
         <v>-29.2</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="H19" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="I19" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="8" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="8" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="8" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5147,58 +5218,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="F20" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="G20" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="H20" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="I20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="8" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="8" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="8" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5218,58 +5290,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="F21" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <v>-11.3</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="H21" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="I21" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="8" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="8" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="8" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5289,58 +5362,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="F22" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="G22" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="H22" s="9" t="n">
         <v>9.5</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="I22" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="8" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="8" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="8" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="8" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5360,58 +5434,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="F23" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="G23" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="H23" s="9" t="n">
         <v>-7.6</v>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="I23" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" s="8" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="8" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="8" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="8" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="8" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="8" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5431,58 +5506,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="F24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="G24" s="9" t="n">
         <v>9.1</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="H24" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="I24" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="8" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="8" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="8" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="8" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="8" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="8" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5502,58 +5578,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="F25" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="G25" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="H25" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="I25" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="8" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="8" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="8" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="8" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5573,58 +5650,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="F26" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="G26" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="G26" s="8" t="n">
+      <c r="H26" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="I26" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="8" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="8" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="8" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="8" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="8" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5644,58 +5722,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="F27" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="G27" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="H27" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="I27" s="9" t="n">
         <v>48.2</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="8" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="8" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="8" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="8" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5715,58 +5794,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="F28" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="G28" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="H28" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="I28" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="8" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="8" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="8" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="8" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5786,58 +5866,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="F29" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="G29" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="H29" s="9" t="n">
         <v>-7.7</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="I29" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>16</v>
       </c>
-      <c r="J29" s="8" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="8" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="8" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5857,58 +5938,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="F30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="G30" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="H30" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="I30" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="8" t="n">
+      <c r="K30" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="M30" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="8" t="n">
+      <c r="O30" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="8" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-14.4</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="8" t="n">
+      <c r="S30" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="8" t="n">
+      <c r="U30" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5928,58 +6010,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="F31" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="G31" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="G31" s="8" t="n">
+      <c r="H31" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="I31" s="9" t="n">
         <v>-6.3</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="K31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="M31" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="O31" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="8" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-17.8</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="8" t="n">
+      <c r="U31" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5999,56 +6082,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="F32" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="G32" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="G32" s="8" t="n">
+      <c r="H32" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="I32" s="9" t="n">
         <v>-15</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="8" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="8" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="8" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="8" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6066,58 +6150,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>반도체 +0.7%. 전자기술 순강도+3, AI반도체 강세. 화훙반도체 장중 신고가 터치</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="F33" s="9" t="n">
         <v>-6.5</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="G33" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="H33" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="I33" s="9" t="n">
         <v>57.4</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="8" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="8" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="8" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6137,58 +6226,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>테크 -2.0%. 기술주 전반 조정, 성장주 소프트</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="F34" s="9" t="n">
         <v>-7.1</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="G34" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="H34" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="I34" s="9" t="n">
         <v>36.7</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="8" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="8" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="8" t="n">
+      <c r="U34" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6208,58 +6302,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>5G통신 -4.2%(1D 최약). 통신장비 급락, 성장 테마 매도</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="F35" s="9" t="n">
         <v>-11.5</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="G35" s="9" t="n">
         <v>-20.9</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="H35" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="I35" s="9" t="n">
         <v>39.8</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="8" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="8" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="8" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="8" t="n">
+      <c r="U35" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6279,56 +6378,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>신에너지차 -1.7%. 부진 지속, 3M -22.9% 약세 흐름</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="F36" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="G36" s="9" t="n">
         <v>-17.5</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="H36" s="9" t="n">
         <v>-22.9</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="I36" s="9" t="n">
         <v>-17</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" s="8" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="8" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="8" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="8" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6346,58 +6450,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>방산 -0.6%. 약세, 3M -24% 낙폭 확대 국면</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="F37" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="G37" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="H37" s="9" t="n">
         <v>-24</v>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="I37" s="9" t="n">
         <v>-21.1</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="8" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="8" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="8" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="8" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="8" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="8" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6417,56 +6526,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>태양광 +0.6%. 소폭 반등, 다만 3M -24.5% 약세 지속</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="F38" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="G38" s="9" t="n">
         <v>-17.8</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="H38" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="I38" s="9" t="n">
         <v>-14.8</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="8" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="8" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="8" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="8" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="8" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6484,58 +6598,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>백주 +1.2%. 소비 반등, 1M +7.8% 저평가 매수</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="F39" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="G39" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="H39" s="9" t="n">
         <v>-11.2</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="I39" s="9" t="n">
         <v>-19.8</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>11</v>
       </c>
-      <c r="J39" s="8" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="8" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="8" t="n">
+      <c r="U39" s="9" t="n">
         <v>302.8</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6555,58 +6674,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>은행 +1.1%. 금융 방어 강세, 배당 매력 부각</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="F40" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="G40" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="H40" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="I40" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="8" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="8" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="8" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="8" t="n">
+      <c r="U40" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6626,58 +6750,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>유색금속 +3.4%(1D 최강). 구리값 급등, 시부광업 +7.8% 견인</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="F41" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="G41" s="9" t="n">
         <v>-10.5</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="H41" s="9" t="n">
         <v>-18.9</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="I41" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>7</v>
       </c>
-      <c r="J41" s="8" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="8" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="8" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="8" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="8" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="8" t="n">
+      <c r="U41" s="9" t="n">
         <v>41.8</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6697,58 +6826,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>부동산 +1.2%. 반등하나 3M -17.2% 약세 국면 유지</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="F42" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="G42" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="H42" s="9" t="n">
         <v>-17.2</v>
       </c>
-      <c r="H42" s="8" t="n">
+      <c r="I42" s="9" t="n">
         <v>-22.7</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="8" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="8" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="8" t="n">
+      <c r="U42" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6768,58 +6902,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>증권 -0.8%. 소폭 약세, 거래대금 관망</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="F43" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="G43" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="H43" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="I43" s="9" t="n">
         <v>-8</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>6</v>
       </c>
-      <c r="J43" s="8" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="8" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="8" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="8" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="8" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6839,58 +6978,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>의약 +0.3%. 보합권, 1M +13.2% 반등 흐름 유지</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="F44" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="G44" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="G44" s="8" t="n">
+      <c r="H44" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="H44" s="8" t="n">
+      <c r="I44" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="8" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="8" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="8" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="8" t="n">
+      <c r="U44" s="9" t="n">
         <v>58.4</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6910,58 +7054,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>소비 +0.6%. 소폭 강세, 1M +9.1% 회복 지속</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E45" s="8" t="n">
+      <c r="F45" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="G45" s="9" t="n">
         <v>9.1</v>
       </c>
-      <c r="G45" s="8" t="n">
+      <c r="H45" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="H45" s="8" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15.1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>9</v>
       </c>
-      <c r="J45" s="8" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="8" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="8" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="8" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="8" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="8" t="n">
+      <c r="U45" s="9" t="n">
         <v>72.7</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6973,7 +7122,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-4.2"/>
@@ -6985,7 +7134,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-11.5"/>
@@ -6997,7 +7146,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-29.2"/>
@@ -7009,7 +7158,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-24.5"/>
@@ -7021,7 +7170,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-22.7"/>
@@ -7033,7 +7182,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7045,7 +7194,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7057,7 +7206,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7069,7 +7218,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7081,7 +7230,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7093,7 +7242,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7249,9 +7398,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
-        <is>
-          <t>Cursor AI 인수 희석+8/6 락업만료(9억주) 매도압력 -6.7%</t>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>(스페이스X 주식 프록시): 8/6 락업 만료 임박·고평가(P/S 64배) 부담, 지분 희석 우려로 하락</t>
         </is>
       </c>
     </row>
@@ -7304,9 +7453,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>실적 상회에도 $14억 인수 발표 불안 -4.2%</t>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>(산업용 커넥터·센서): Q3 실적 상회에도 Astrodyne TDI $14억 인수 발표 후 유기성장 둔화 우려</t>
         </is>
       </c>
     </row>
@@ -7357,9 +7506,9 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>AI 광고기술 경쟁심화 우려, 섹터 수급 부진</t>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>(모바일 광고 플랫폼·AXON AI): AXON 셀프서브 전환 마진 희석 우려·CEO 지분매각, 광고 경쟁 심화</t>
         </is>
       </c>
     </row>
@@ -7410,9 +7559,9 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>7/29 실적 앞두고 이익감소 전망·HVAC 수요둔화 우려</t>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>(HVAC 유통): Q2 실적(7/29) 앞두고 2026 HVAC 수요 부진 신호 재부각, 섹터 약세 수급</t>
         </is>
       </c>
     </row>
@@ -7467,9 +7616,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>매출 상회에도 수술건수 둔화(12% YoY)·ACA 축소 우려</t>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>(로봇수술 시스템·다빈치): Q2 매출 상회에도 2026 시술건수 성장 가이던스 하향(국제 선택수술 둔화)</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7673,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -7573,7 +7722,7 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -7624,7 +7773,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7675,9 +7824,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>Plozasiran 3상서 중성지방 79~81% 감소 호성적 발표 +19%</t>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>(RNAi 신약개발): 플로자시란 고중성지방혈증 3상(SHASTA-3/4) 성공, 중성지방 79~81% 감소</t>
         </is>
       </c>
     </row>
@@ -7728,9 +7877,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>2Q EPS $2.76(예상 상회)+FY26 가이던스 상향 +10%</t>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>(철도·화물 운송장비): Q2 매출 $31.8억(+17.5%)·EPS $2.76 상회, 수주잔고 $309억(+41.7%)에 가이던스 상향</t>
         </is>
       </c>
     </row>
@@ -7785,9 +7934,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>BofA·바클레이즈 등 목표가 일제 상향, 호실적 기대</t>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>(복합 자동차딜러·상용차): Q2 실적 상회·연간 가이던스 상향, BofA·바클레이즈 등 목표가 일제 상향</t>
         </is>
       </c>
     </row>
@@ -7838,9 +7987,9 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>독일 EnBW 등과 신규 LNG 판매계약 확대</t>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>(미국 LNG 수출): CP2 LNG 2단계 FID·$86억 PF 완료, 2026 EBITDA 가이던스 $82~85억 재확인</t>
         </is>
       </c>
     </row>
@@ -7891,9 +8040,9 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>WAB 호실적 halo+실적 기대(단독 촉매 미확인)</t>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>(대형트럭 제조·켄워스·피터빌트): 6월 Class8 트럭 수주 전년비 +230% 급증, 수요 회복 기대</t>
         </is>
       </c>
     </row>
@@ -7944,7 +8093,7 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7993,7 +8142,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8046,7 +8195,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -8093,7 +8242,7 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8140,7 +8289,7 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -8193,7 +8342,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8246,7 +8395,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -8299,7 +8448,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -8352,7 +8501,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -8405,7 +8554,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -8454,7 +8603,7 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -8507,7 +8656,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -8560,7 +8709,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="9" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -8613,7 +8762,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -8666,7 +8815,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -8719,7 +8868,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>(전일) General Mills·월마트 재생농업 제휴 발표+BMO 목표가 상향</t>
         </is>
@@ -8772,7 +8921,7 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>(전일) AES(글로벌 발전·재생에너지 유틸리티): 7/15 분기배당 선언+재생에너지 확장, 7/30 실적 기대</t>
         </is>
@@ -8827,7 +8976,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -8880,7 +9029,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>(전일) 정제 업황 호조, Raymond James TP $235 상향·정유 동반 강세</t>
         </is>
@@ -8937,7 +9086,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -8990,7 +9139,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="9" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -9043,7 +9192,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M36" s="9" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -9096,7 +9245,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -9149,7 +9298,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M38" s="9" t="inlineStr">
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>(전일) 정제마진 강세 지속, 애널리스트 목표가 상향 랠리</t>
         </is>
@@ -9206,7 +9355,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M39" s="9" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -9259,7 +9408,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="9" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -9312,7 +9461,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M41" s="9" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M41"/>
@@ -9462,9 +9611,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
-        <is>
-          <t>금리상승·엔약세 수혜 금융 로테이션, 은행주 신고가</t>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>(우편계열 은행): 일본 장기금리 약 29년래 고수준(~2.8%) 이자마진 확대 기대로 금융섹터 매수 유입</t>
         </is>
       </c>
     </row>
@@ -9519,9 +9668,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>금리상승 수혜 메가뱅크 강세, 신고가</t>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>(3대 메가뱅크): 도카이도쿄 목표가 5830→8140엔 대폭 상향, 일은 추가 금리인상 기대에 평가 상승</t>
         </is>
       </c>
     </row>
@@ -9576,9 +9725,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>금융 로테이션 동반 신탁은행 신고가</t>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>(신탁·자산운용 은행): 장기금리 상승(~2.8%, 29년래 고)에 자금수익 개선 기대로 은행섹터 동반 상승</t>
         </is>
       </c>
     </row>
@@ -9633,9 +9782,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>금리·운용수익 개선 기대 손보 신고가</t>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>(손해보험 지주): 장기금리 상승에 보험자산 운용이익 개선 기대, 금융섹터 강세에 동반 신고가</t>
         </is>
       </c>
     </row>
@@ -9690,9 +9839,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>금융 로테이션 속 리스·금융 신고가</t>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>(종합금융·리스 지주): FY3/2026 순이익 +27% 최고 실적 호조에 금리상승 환경 겹쳐 매수세 지속</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9892,7 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -9796,7 +9945,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -9845,7 +9994,7 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>(전일) 캐논(카메라·사무기기·반도체 노광): 광범위 자율반등+7/27 결산 앞둔 매수</t>
         </is>
@@ -9898,7 +10047,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>(전일) 닛폰스틸(일본 최대 철강): US스틸 철강가 호조·FY27 이익 1000억엔 기여 기대로 자율반등</t>
         </is>
@@ -10048,9 +10197,9 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr">
-        <is>
-          <t>경기민감 항공, 여객수요 회복 기대 신고가</t>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>(홍콩 국적 항공사): 캐세이퍼시픽, 상반기 순이익 60~65억 홍콩달러(전년비 최대 +76%) 예고, 여객·화물 호조</t>
         </is>
       </c>
     </row>
@@ -10101,9 +10250,9 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>통신 방어주로 테크 약세장서 상대 강세</t>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>(홍콩 통신사): HKT, 특별한 뉴스 없음(방어주 성격·AI 데이터센터 인프라 테마 수급 추정)</t>
         </is>
       </c>
     </row>
@@ -10154,9 +10303,9 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>바이오테크 개별 강세(섹터 수급)</t>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>(글로벌 항암제 개발): 비원메디슨, 특별한 뉴스 없음(브루킨사·소노로토클락스 파이프라인 모멘텀 지속 추정)</t>
         </is>
       </c>
     </row>
@@ -10211,9 +10360,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>금리·배당 매력 금융, HSBC 신고가</t>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>(글로벌 대형 은행): HSBC, JP모건 투자의견 중립 상향·목표가 1380펜스, 항성은행 완전자회사화 시너지 기대</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10417,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>(전일) SITC(아시아 역내 컨테이너 해운): 컨테이너 운임 4년래 고점·중동 리스크로 역내 운임 반등 수혜</t>
         </is>
@@ -10422,9 +10571,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
-        <is>
-          <t>데이터센터 400G 스위치 수요+상반기 순익 +33~66% 예증, AI네트워킹 주도 +13.7%</t>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>(기업용 네트워크 스위치·라우터): H1 귀속순이익 33~66% 증가 예고·AI 데이터센터 스위치 수주잔고 최고로 상한가</t>
         </is>
       </c>
     </row>
@@ -10477,9 +10626,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>이더넷 스위치칩 AI수혜 테마, 반도체 섹터 강세 동반 +8.9%</t>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>(이더넷 스위치 칩): 중전계 관계사 연간 거래한도 6억→22억 위안 대폭 상향, 국산 AI연산 스위치칩 수요 급증</t>
         </is>
       </c>
     </row>
@@ -10530,9 +10679,9 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>상반기 순익 +114~130% 예증(구리·금 강세 수혜) +7.8%</t>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>(구리·아연·몰리브덴 광산): H1 귀속순이익 114~130% 증가 예고(구리·귀금속 급등)·유색금속 섹터 동반 강세</t>
         </is>
       </c>
     </row>
@@ -10587,9 +10736,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>AI서버 상반기 순익 +226~288% 예증 후 섹터 강세 유지</t>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>(AI 서버·고성능컴퓨팅·인스퍼): H1 귀속순이익 226~288% 급증 예고 이후 AI연산 섹터 수급 지속 유입</t>
         </is>
       </c>
     </row>
@@ -10644,9 +10793,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>미 상무부 램리서치·AMAT·KLA에 화홍향 장비 출하중단 지시 -1.9%</t>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>(성숙공정 파운드리·화훙): 반도체 섹터 강세·골드만삭스 목표가 대폭 상향으로 장중 신고가, 종가는 소폭 하락</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10850,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>상반기 순이익 최대 +123% 실적예고·AI서버 수주·紫光 지분정합 완료로 연속 상한가</t>
         </is>
